--- a/artfynd/A 26461-2025 artfynd.xlsx
+++ b/artfynd/A 26461-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>105069974</v>
       </c>
       <c r="B2" t="n">
-        <v>103357</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105715</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>712288.1510302525</v>
+        <v>712288</v>
       </c>
       <c r="R2" t="n">
-        <v>6373645.203560951</v>
+        <v>6373645</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>1985-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 26461-2025 artfynd.xlsx
+++ b/artfynd/A 26461-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105069974</v>
       </c>
       <c r="B2" t="n">
-        <v>105715</v>
+        <v>105724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26461-2025 artfynd.xlsx
+++ b/artfynd/A 26461-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105069974</v>
       </c>
       <c r="B2" t="n">
-        <v>105724</v>
+        <v>105736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26461-2025 artfynd.xlsx
+++ b/artfynd/A 26461-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105069974</v>
       </c>
       <c r="B2" t="n">
-        <v>105736</v>
+        <v>105745</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26461-2025 artfynd.xlsx
+++ b/artfynd/A 26461-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105069974</v>
       </c>
       <c r="B2" t="n">
-        <v>105745</v>
+        <v>105750</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26461-2025 artfynd.xlsx
+++ b/artfynd/A 26461-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105069974</v>
       </c>
       <c r="B2" t="n">
-        <v>105750</v>
+        <v>105778</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26461-2025 artfynd.xlsx
+++ b/artfynd/A 26461-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105069974</v>
       </c>
       <c r="B2" t="n">
-        <v>105778</v>
+        <v>105784</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26461-2025 artfynd.xlsx
+++ b/artfynd/A 26461-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105069974</v>
       </c>
       <c r="B2" t="n">
-        <v>105784</v>
+        <v>105791</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26461-2025 artfynd.xlsx
+++ b/artfynd/A 26461-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105069974</v>
       </c>
       <c r="B2" t="n">
-        <v>105791</v>
+        <v>105795</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26461-2025 artfynd.xlsx
+++ b/artfynd/A 26461-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105069974</v>
       </c>
       <c r="B2" t="n">
-        <v>105795</v>
+        <v>105802</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26461-2025 artfynd.xlsx
+++ b/artfynd/A 26461-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105069974</v>
       </c>
       <c r="B2" t="n">
-        <v>105805</v>
+        <v>105810</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26461-2025 artfynd.xlsx
+++ b/artfynd/A 26461-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105069974</v>
       </c>
       <c r="B2" t="n">
-        <v>105810</v>
+        <v>105818</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
